--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R9" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B10" t="n">
-        <v>79854</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R10" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,48 +1621,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793077</v>
+        <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>80398</v>
+        <v>79883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701464</v>
+        <v>701359</v>
       </c>
       <c r="R11" t="n">
-        <v>7413668</v>
+        <v>7413842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,13 +1700,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1727,45 +1723,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793073</v>
+        <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>79883</v>
+        <v>80398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701359</v>
+        <v>701464</v>
       </c>
       <c r="R12" t="n">
-        <v>7413842</v>
+        <v>7413668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1805,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793073</v>
+        <v>131793079</v>
       </c>
       <c r="B11" t="n">
-        <v>79883</v>
+        <v>79343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,34 +1632,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701359</v>
+        <v>701423</v>
       </c>
       <c r="R11" t="n">
-        <v>7413842</v>
+        <v>7413735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,12 +1703,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793079</v>
+        <v>131793073</v>
       </c>
       <c r="B13" t="n">
-        <v>79343</v>
+        <v>79883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,37 +1844,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701423</v>
+        <v>701359</v>
       </c>
       <c r="R13" t="n">
-        <v>7413735</v>
+        <v>7413842</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,13 +1912,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1935,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793066</v>
+        <v>131793071</v>
       </c>
       <c r="B14" t="n">
-        <v>80405</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R14" t="n">
-        <v>7413783</v>
+        <v>7413840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793071</v>
+        <v>131793066</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>80405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701357</v>
+        <v>701339</v>
       </c>
       <c r="R15" t="n">
-        <v>7413840</v>
+        <v>7413783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79854</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R9" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R10" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793079</v>
+        <v>131793077</v>
       </c>
       <c r="B11" t="n">
-        <v>79343</v>
+        <v>80398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701423</v>
+        <v>701464</v>
       </c>
       <c r="R11" t="n">
-        <v>7413735</v>
+        <v>7413668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1727,48 +1727,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793077</v>
+        <v>131793073</v>
       </c>
       <c r="B12" t="n">
-        <v>80398</v>
+        <v>79883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701464</v>
+        <v>701359</v>
       </c>
       <c r="R12" t="n">
-        <v>7413668</v>
+        <v>7413842</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,13 +1806,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1833,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793073</v>
+        <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>79883</v>
+        <v>79343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,34 +1840,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701359</v>
+        <v>701423</v>
       </c>
       <c r="R13" t="n">
-        <v>7413842</v>
+        <v>7413735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,12 +1911,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131793068</v>
       </c>
       <c r="B2" t="n">
-        <v>78271</v>
+        <v>78273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131793078</v>
       </c>
       <c r="B3" t="n">
-        <v>78667</v>
+        <v>78669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>131793069</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131793065</v>
       </c>
       <c r="B6" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131793072</v>
       </c>
       <c r="B7" t="n">
-        <v>79343</v>
+        <v>79345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131793070</v>
       </c>
       <c r="B8" t="n">
-        <v>79343</v>
+        <v>79345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79856</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R9" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B10" t="n">
-        <v>79854</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R10" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,48 +1621,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793077</v>
+        <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>80398</v>
+        <v>79885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701464</v>
+        <v>701359</v>
       </c>
       <c r="R11" t="n">
-        <v>7413668</v>
+        <v>7413842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,13 +1700,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1727,45 +1723,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793073</v>
+        <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>79883</v>
+        <v>80400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701359</v>
+        <v>701464</v>
       </c>
       <c r="R12" t="n">
-        <v>7413842</v>
+        <v>7413668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1805,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
         <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>79343</v>
+        <v>79345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793071</v>
+        <v>131793066</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>80407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701357</v>
+        <v>701339</v>
       </c>
       <c r="R14" t="n">
-        <v>7413840</v>
+        <v>7413783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793066</v>
+        <v>131793071</v>
       </c>
       <c r="B15" t="n">
-        <v>80405</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R15" t="n">
-        <v>7413783</v>
+        <v>7413840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R9" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>79856</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R10" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1621,45 +1621,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793073</v>
+        <v>131793077</v>
       </c>
       <c r="B11" t="n">
-        <v>79885</v>
+        <v>80400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701359</v>
+        <v>701464</v>
       </c>
       <c r="R11" t="n">
-        <v>7413842</v>
+        <v>7413668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,12 +1703,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1723,32 +1727,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793077</v>
+        <v>131793079</v>
       </c>
       <c r="B12" t="n">
-        <v>80400</v>
+        <v>79345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701464</v>
+        <v>701423</v>
       </c>
       <c r="R12" t="n">
-        <v>7413668</v>
+        <v>7413735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793079</v>
+        <v>131793073</v>
       </c>
       <c r="B13" t="n">
-        <v>79345</v>
+        <v>79885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,37 +1844,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701423</v>
+        <v>701359</v>
       </c>
       <c r="R13" t="n">
-        <v>7413735</v>
+        <v>7413842</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,13 +1912,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>79856</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R9" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B10" t="n">
-        <v>79856</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R10" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R9" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>79856</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R10" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,48 +1621,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793077</v>
+        <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>80400</v>
+        <v>79885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701464</v>
+        <v>701359</v>
       </c>
       <c r="R11" t="n">
-        <v>7413668</v>
+        <v>7413842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,13 +1700,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1727,32 +1723,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793079</v>
+        <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>79345</v>
+        <v>80400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701423</v>
+        <v>701464</v>
       </c>
       <c r="R12" t="n">
-        <v>7413735</v>
+        <v>7413668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1833,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793073</v>
+        <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>79885</v>
+        <v>79345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,34 +1840,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701359</v>
+        <v>701423</v>
       </c>
       <c r="R13" t="n">
-        <v>7413842</v>
+        <v>7413735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,12 +1911,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131793068</v>
       </c>
       <c r="B2" t="n">
-        <v>78273</v>
+        <v>78276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131793078</v>
       </c>
       <c r="B3" t="n">
-        <v>78669</v>
+        <v>78672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131793064</v>
       </c>
       <c r="B4" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>131793069</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131793065</v>
       </c>
       <c r="B6" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131793072</v>
       </c>
       <c r="B7" t="n">
-        <v>79345</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131793070</v>
       </c>
       <c r="B8" t="n">
-        <v>79345</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R9" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>79859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R10" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,7 +1624,7 @@
         <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>79345</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793066</v>
+        <v>131793071</v>
       </c>
       <c r="B14" t="n">
-        <v>80407</v>
+        <v>79269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R14" t="n">
-        <v>7413783</v>
+        <v>7413840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793071</v>
+        <v>131793066</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>80410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701357</v>
+        <v>701339</v>
       </c>
       <c r="R15" t="n">
-        <v>7413840</v>
+        <v>7413783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131793068</v>
       </c>
       <c r="B2" t="n">
-        <v>78276</v>
+        <v>78281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131793078</v>
       </c>
       <c r="B3" t="n">
-        <v>78672</v>
+        <v>78677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>131793069</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131793065</v>
       </c>
       <c r="B6" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131793072</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>79353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131793070</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>79348</v>
+        <v>79353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793071</v>
+        <v>131793066</v>
       </c>
       <c r="B14" t="n">
-        <v>79269</v>
+        <v>80415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701357</v>
+        <v>701339</v>
       </c>
       <c r="R14" t="n">
-        <v>7413840</v>
+        <v>7413783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793066</v>
+        <v>131793071</v>
       </c>
       <c r="B15" t="n">
-        <v>80410</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R15" t="n">
-        <v>7413783</v>
+        <v>7413840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131793068</v>
       </c>
       <c r="B2" t="n">
-        <v>78281</v>
+        <v>78283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131793078</v>
       </c>
       <c r="B3" t="n">
-        <v>78677</v>
+        <v>78679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>131793069</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131793065</v>
       </c>
       <c r="B6" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131793072</v>
       </c>
       <c r="B7" t="n">
-        <v>79353</v>
+        <v>79355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131793070</v>
       </c>
       <c r="B8" t="n">
-        <v>79353</v>
+        <v>79355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>79353</v>
+        <v>79355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>131793066</v>
       </c>
       <c r="B14" t="n">
-        <v>80415</v>
+        <v>80417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>131793071</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131793068</v>
       </c>
       <c r="B2" t="n">
-        <v>78322</v>
+        <v>78324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131793078</v>
       </c>
       <c r="B3" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>131793069</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131793065</v>
       </c>
       <c r="B6" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131793072</v>
       </c>
       <c r="B7" t="n">
-        <v>79394</v>
+        <v>79396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131793070</v>
       </c>
       <c r="B8" t="n">
-        <v>79394</v>
+        <v>79396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793067</v>
+        <v>131793074</v>
       </c>
       <c r="B9" t="n">
-        <v>79905</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701421</v>
+        <v>701463</v>
       </c>
       <c r="R9" t="n">
-        <v>7413685</v>
+        <v>7413719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793074</v>
+        <v>131793067</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>79907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701463</v>
+        <v>701421</v>
       </c>
       <c r="R10" t="n">
-        <v>7413719</v>
+        <v>7413685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793079</v>
+        <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>79394</v>
+        <v>79936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,37 +1632,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701423</v>
+        <v>701359</v>
       </c>
       <c r="R11" t="n">
-        <v>7413735</v>
+        <v>7413842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,13 +1700,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1727,45 +1723,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793073</v>
+        <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>79934</v>
+        <v>80451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701359</v>
+        <v>701464</v>
       </c>
       <c r="R12" t="n">
-        <v>7413842</v>
+        <v>7413668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1805,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1829,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793077</v>
+        <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>80449</v>
+        <v>79396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701464</v>
+        <v>701423</v>
       </c>
       <c r="R13" t="n">
-        <v>7413668</v>
+        <v>7413735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>131793066</v>
       </c>
       <c r="B14" t="n">
-        <v>80456</v>
+        <v>80458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>131793071</v>
       </c>
       <c r="B15" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793073</v>
+        <v>131793079</v>
       </c>
       <c r="B11" t="n">
-        <v>79936</v>
+        <v>79396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,34 +1632,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701359</v>
+        <v>701423</v>
       </c>
       <c r="R11" t="n">
-        <v>7413842</v>
+        <v>7413735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,12 +1703,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1723,48 +1727,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793077</v>
+        <v>131793073</v>
       </c>
       <c r="B12" t="n">
-        <v>80451</v>
+        <v>79936</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701464</v>
+        <v>701359</v>
       </c>
       <c r="R12" t="n">
-        <v>7413668</v>
+        <v>7413842</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,13 +1806,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1829,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793079</v>
+        <v>131793077</v>
       </c>
       <c r="B13" t="n">
-        <v>79396</v>
+        <v>80451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701423</v>
+        <v>701464</v>
       </c>
       <c r="R13" t="n">
-        <v>7413735</v>
+        <v>7413668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -1935,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793066</v>
+        <v>131793071</v>
       </c>
       <c r="B14" t="n">
-        <v>80458</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R14" t="n">
-        <v>7413783</v>
+        <v>7413840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793071</v>
+        <v>131793066</v>
       </c>
       <c r="B15" t="n">
-        <v>79317</v>
+        <v>80458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701357</v>
+        <v>701339</v>
       </c>
       <c r="R15" t="n">
-        <v>7413840</v>
+        <v>7413783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1190,14 +1190,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131793072</v>
+        <v>131793070</v>
       </c>
       <c r="B7" t="n">
         <v>79396</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701463</v>
+        <v>701469</v>
       </c>
       <c r="R7" t="n">
-        <v>7413669</v>
+        <v>7413713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,14 +1296,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131793070</v>
+        <v>131793072</v>
       </c>
       <c r="B8" t="n">
         <v>79396</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701469</v>
+        <v>701463</v>
       </c>
       <c r="R8" t="n">
-        <v>7413713</v>
+        <v>7413669</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793079</v>
+        <v>131793073</v>
       </c>
       <c r="B11" t="n">
-        <v>79396</v>
+        <v>79936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,37 +1632,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701423</v>
+        <v>701359</v>
       </c>
       <c r="R11" t="n">
-        <v>7413735</v>
+        <v>7413842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,13 +1700,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1720,52 +1716,55 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793073</v>
+        <v>131793077</v>
       </c>
       <c r="B12" t="n">
-        <v>79936</v>
+        <v>80451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701359</v>
+        <v>701464</v>
       </c>
       <c r="R12" t="n">
-        <v>7413842</v>
+        <v>7413668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1805,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1822,39 +1822,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793077</v>
+        <v>131793079</v>
       </c>
       <c r="B13" t="n">
-        <v>80451</v>
+        <v>79396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701464</v>
+        <v>701423</v>
       </c>
       <c r="R13" t="n">
-        <v>7413668</v>
+        <v>7413735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1928,39 +1928,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793071</v>
+        <v>131793066</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>80458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701357</v>
+        <v>701339</v>
       </c>
       <c r="R14" t="n">
-        <v>7413840</v>
+        <v>7413783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2034,39 +2034,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793066</v>
+        <v>131793071</v>
       </c>
       <c r="B15" t="n">
-        <v>80458</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R15" t="n">
-        <v>7413783</v>
+        <v>7413840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131793068</v>
+        <v>131793070</v>
       </c>
       <c r="B2" t="n">
-        <v>78324</v>
+        <v>79452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701422</v>
+        <v>701469</v>
       </c>
       <c r="R2" t="n">
-        <v>7413682</v>
+        <v>7413713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131793078</v>
+        <v>131793072</v>
       </c>
       <c r="B3" t="n">
-        <v>78720</v>
+        <v>79452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701422</v>
+        <v>701463</v>
       </c>
       <c r="R3" t="n">
-        <v>7413688</v>
+        <v>7413669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,52 +880,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131793064</v>
+        <v>131793079</v>
       </c>
       <c r="B4" t="n">
-        <v>5199</v>
+        <v>79452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701357</v>
+        <v>701423</v>
       </c>
       <c r="R4" t="n">
-        <v>7413835</v>
+        <v>7413735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +969,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -982,17 +986,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131793069</v>
+        <v>131793065</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>83222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,37 +1004,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701374</v>
+        <v>701359</v>
       </c>
       <c r="R5" t="n">
-        <v>7413748</v>
+        <v>7413837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,13 +1072,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1088,52 +1088,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131793065</v>
+        <v>131793069</v>
       </c>
       <c r="B6" t="n">
-        <v>83163</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701359</v>
+        <v>701374</v>
       </c>
       <c r="R6" t="n">
-        <v>7413837</v>
+        <v>7413748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1177,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1190,39 +1194,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131793070</v>
+        <v>131793071</v>
       </c>
       <c r="B7" t="n">
-        <v>79396</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701469</v>
+        <v>701357</v>
       </c>
       <c r="R7" t="n">
-        <v>7413713</v>
+        <v>7413840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1289,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Stamtät, lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1296,39 +1300,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131793072</v>
+        <v>131793074</v>
       </c>
       <c r="B8" t="n">
-        <v>79396</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,7 +1348,7 @@
         <v>701463</v>
       </c>
       <c r="R8" t="n">
-        <v>7413669</v>
+        <v>7413719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,17 +1406,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131793074</v>
+        <v>131793078</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>78776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701463</v>
+        <v>701422</v>
       </c>
       <c r="R9" t="n">
-        <v>7413719</v>
+        <v>7413688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,17 +1512,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131793067</v>
+        <v>131793073</v>
       </c>
       <c r="B10" t="n">
-        <v>79907</v>
+        <v>79992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,37 +1530,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701421</v>
+        <v>701359</v>
       </c>
       <c r="R10" t="n">
-        <v>7413685</v>
+        <v>7413842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,13 +1598,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1614,52 +1614,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131793073</v>
+        <v>131793077</v>
       </c>
       <c r="B11" t="n">
-        <v>79936</v>
+        <v>80493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701359</v>
+        <v>701464</v>
       </c>
       <c r="R11" t="n">
-        <v>7413842</v>
+        <v>7413668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,12 +1703,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1716,17 +1720,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131793077</v>
+        <v>131793066</v>
       </c>
       <c r="B12" t="n">
-        <v>80451</v>
+        <v>80500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701464</v>
+        <v>701339</v>
       </c>
       <c r="R12" t="n">
-        <v>7413668</v>
+        <v>7413783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
+          <t>Stamtät, lövrik barrblandad barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1822,17 +1826,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131793079</v>
+        <v>131793068</v>
       </c>
       <c r="B13" t="n">
-        <v>79396</v>
+        <v>78377</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701423</v>
+        <v>701422</v>
       </c>
       <c r="R13" t="n">
-        <v>7413735</v>
+        <v>7413682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1921,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles barrsumpskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1928,17 +1932,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131793066</v>
+        <v>131793064</v>
       </c>
       <c r="B14" t="n">
-        <v>80458</v>
+        <v>5201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,37 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Naturskog väster om Ládnjoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701339</v>
+        <v>701357</v>
       </c>
       <c r="R14" t="n">
-        <v>7413783</v>
+        <v>7413835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,13 +2018,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandad barrskog</t>
+          <t>Lågproduktiv kantzon mellan stamtät, hänglavsrik barrnaturskog och gles barrsumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131793071</v>
+        <v>131793067</v>
       </c>
       <c r="B15" t="n">
-        <v>79317</v>
+        <v>79963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701357</v>
+        <v>701421</v>
       </c>
       <c r="R15" t="n">
-        <v>7413840</v>
+        <v>7413685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Stamtät, lövrik barrblandskog</t>
+          <t>Lövrik barrblandskog med rikligt inslag av brandstubbar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 60161-2025 artfynd.xlsx
+++ b/artfynd/A 60161-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793072</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793065</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793069</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793071</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793078</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793073</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793077</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793066</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793068</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2038,6 +2103,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793064</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,8 +2214,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131793067</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>